--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/2331-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/2331-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A134730B-8810-4B34-859D-F2640E5B2E88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BA0939B5-A9F0-4444-B8C6-21FBAA2CF978}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{E3712A0E-24E5-4643-8D78-58702B1C3826}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{7EB0BD46-65D1-43BD-BF21-5E48648A7AB4}"/>
   </bookViews>
   <sheets>
     <sheet name="2331-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1553,26 +1553,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61E57D12-DCE1-4A04-9FD9-7D7ECC67A86B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03FB91AB-A425-42C3-AB06-D419EE1CE612}">
   <dimension ref="A1:X54"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.25" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1606,7 +1606,7 @@
       <c r="W1" s="30"/>
       <c r="X1" s="22"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1642,7 +1642,7 @@
       <c r="W2" s="32"/>
       <c r="X2" s="33"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="X3" s="36"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1762,7 +1762,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="37">
         <v>2024</v>
       </c>
@@ -1834,7 +1834,7 @@
         <v>1.59</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1908,7 +1908,7 @@
         <v>1.59</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>29</v>
       </c>
@@ -1982,7 +1982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>29</v>
       </c>
@@ -2056,7 +2056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="39">
         <v>2023</v>
       </c>
@@ -2128,7 +2128,7 @@
         <v>4.68</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>29</v>
       </c>
@@ -2202,7 +2202,7 @@
         <v>4.68</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
         <v>29</v>
       </c>
@@ -2276,7 +2276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="37">
         <v>2022</v>
       </c>
@@ -2348,7 +2348,7 @@
         <v>3.93</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>29</v>
       </c>
@@ -2422,7 +2422,7 @@
         <v>3.93</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
         <v>29</v>
       </c>
@@ -2496,7 +2496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>29</v>
       </c>
@@ -2570,7 +2570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="39">
         <v>2021</v>
       </c>
@@ -2642,7 +2642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="16" t="s">
         <v>29</v>
       </c>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="16" t="s">
         <v>29</v>
       </c>
@@ -2790,7 +2790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="16" t="s">
         <v>29</v>
       </c>
@@ -2864,7 +2864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="37">
         <v>2020</v>
       </c>
@@ -2936,7 +2936,7 @@
         <v>5.3</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
         <v>29</v>
       </c>
@@ -3010,7 +3010,7 @@
         <v>5.3</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="11" t="s">
         <v>29</v>
       </c>
@@ -3084,7 +3084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="39">
         <v>2019</v>
       </c>
@@ -3156,7 +3156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="16" t="s">
         <v>29</v>
       </c>
@@ -3230,7 +3230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="16" t="s">
         <v>29</v>
       </c>
@@ -3304,7 +3304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="37">
         <v>2018</v>
       </c>
@@ -3376,7 +3376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="39">
         <v>2017</v>
       </c>
@@ -3448,7 +3448,7 @@
         <v>8.51</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="37">
         <v>2016</v>
       </c>
@@ -3520,7 +3520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="39">
         <v>2015</v>
       </c>
@@ -3592,7 +3592,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="37">
         <v>2014</v>
       </c>
@@ -3664,7 +3664,7 @@
         <v>32.5</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="39">
         <v>2013</v>
       </c>
@@ -3736,7 +3736,7 @@
         <v>18.100000000000001</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="37">
         <v>2012</v>
       </c>
@@ -3808,7 +3808,7 @@
         <v>5.52</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="39">
         <v>2011</v>
       </c>
@@ -3880,7 +3880,7 @@
         <v>39.700000000000003</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="37">
         <v>2010</v>
       </c>
@@ -3952,7 +3952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="39">
         <v>2009</v>
       </c>
@@ -4024,7 +4024,7 @@
         <v>4.9800000000000004</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="37">
         <v>2008</v>
       </c>
@@ -4096,7 +4096,7 @@
         <v>4.46</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="39">
         <v>2007</v>
       </c>
@@ -4168,7 +4168,7 @@
         <v>13.1</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="37">
         <v>2006</v>
       </c>
@@ -4240,7 +4240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="39">
         <v>2005</v>
       </c>
@@ -4312,7 +4312,7 @@
         <v>4.22</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="37">
         <v>2004</v>
       </c>
@@ -4384,7 +4384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="39">
         <v>2003</v>
       </c>
@@ -4456,7 +4456,7 @@
         <v>9.85</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="37">
         <v>2002</v>
       </c>
@@ -4528,7 +4528,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="39">
         <v>2001</v>
       </c>
@@ -4600,7 +4600,7 @@
         <v>9.65</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="37">
         <v>2000</v>
       </c>
@@ -4672,7 +4672,7 @@
         <v>11.3</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="39">
         <v>1999</v>
       </c>
@@ -4744,7 +4744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="37">
         <v>1998</v>
       </c>
@@ -4816,7 +4816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="39">
         <v>1997</v>
       </c>
@@ -4888,7 +4888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="37">
         <v>1996</v>
       </c>
@@ -4960,7 +4960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A49" s="39">
         <v>1995</v>
       </c>
@@ -5032,7 +5032,7 @@
         <v>2.84</v>
       </c>
     </row>
-    <row r="50" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A50" s="37">
         <v>1994</v>
       </c>
@@ -5104,7 +5104,7 @@
         <v>10.9</v>
       </c>
     </row>
-    <row r="51" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A51" s="39">
         <v>1993</v>
       </c>
@@ -5176,7 +5176,7 @@
         <v>4.9000000000000004</v>
       </c>
     </row>
-    <row r="52" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A52" s="41">
         <v>1992</v>
       </c>
@@ -5248,7 +5248,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="53" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A53" s="43"/>
       <c r="B53" s="44"/>
       <c r="C53" s="20" t="s">
@@ -5276,7 +5276,7 @@
       <c r="W53" s="50"/>
       <c r="X53" s="46"/>
     </row>
-    <row r="54" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A54" s="39" t="s">
         <v>60</v>
       </c>
